--- a/outputs/daily/hr_rankings_2026-09-24_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-09-24_full.xlsx
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>65.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>48.7</v>
       </c>
       <c r="R3" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>57.5</v>
+        <v>57.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>50.5</v>
       </c>
       <c r="R18" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S18" t="n">
         <v>94.90000000000001</v>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -5504,7 +5504,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>56.8</v>
+        <v>57</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>50.5</v>
       </c>
       <c r="R19" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S19" t="n">
         <v>100</v>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -7395,27 +7395,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>681715</t>
+          <t>683146</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Heriberto Hernández</t>
+          <t>Brett Baty</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-24T18:20:00Z</t>
+          <t>2026-09-24T18:35:00Z</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7425,26 +7425,26 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Matthew Boyd</t>
+          <t>Kumar Rocker</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>571510</t>
+          <t>677958</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>55.3</v>
+        <v>55.5</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7458,26 +7458,26 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>52.5</v>
+        <v>45.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>41.3</v>
+        <v>48.7</v>
       </c>
       <c r="R26" t="n">
-        <v>38.8</v>
+        <v>42.1</v>
       </c>
       <c r="S26" t="n">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U26" t="n">
-        <v>23.4</v>
+        <v>63.3</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -7529,27 +7529,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Contact streak: 7/15 over last 7 games</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 16.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.9% barrel, 17.3 HR allowed</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
@@ -7559,112 +7559,112 @@
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>12.12</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>46.52</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>90.56</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>101.636</t>
+          <t>101.8115</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>0.4588</t>
+          <t>0.4234</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>0.2145</t>
+          <t>0.1798</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>0.3438</t>
+          <t>0.3242</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>74.07</t>
+          <t>75.15</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>44.06</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>46.12</t>
+          <t>35.4</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>0.1972</t>
+          <t>0.1516</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>38.14</t>
+          <t>42.39</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>88.43</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>0.4176</t>
+          <t>0.4392</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
-          <t>0.1601</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr"/>
@@ -7675,27 +7675,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>683146</t>
+          <t>681715</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brett Baty</t>
+          <t>Heriberto Hernández</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-24T18:35:00Z</t>
+          <t>2026-09-24T18:20:00Z</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7705,22 +7705,22 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Kumar Rocker</t>
+          <t>Matthew Boyd</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>571510</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -7738,26 +7738,26 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>45.4</v>
+        <v>52.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>48.7</v>
+        <v>41.3</v>
       </c>
       <c r="R27" t="n">
-        <v>41.1</v>
+        <v>38.8</v>
       </c>
       <c r="S27" t="n">
-        <v>86.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="T27" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U27" t="n">
-        <v>63.3</v>
+        <v>23.4</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -7809,27 +7809,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Contact streak: 7/15 over last 7 games</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.9% barrel, 17.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 16.2 HR allowed</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
@@ -7839,112 +7839,112 @@
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>12.12</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>46.52</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>90.56</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>101.8115</t>
+          <t>101.636</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>0.4234</t>
+          <t>0.4588</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>0.1798</t>
+          <t>0.2145</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>0.3242</t>
+          <t>0.3438</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>75.15</t>
+          <t>74.07</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>44.06</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>35.4</t>
+          <t>46.12</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>30.62</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>0.1516</t>
+          <t>0.1972</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>42.39</t>
+          <t>38.14</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>88.43</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>0.4392</t>
+          <t>0.4176</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.1601</t>
         </is>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>66</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr"/>
@@ -8556,7 +8556,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>54</v>
+        <v>54.2</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>50.5</v>
       </c>
       <c r="R30" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S30" t="n">
         <v>96.59999999999999</v>
@@ -8771,7 +8771,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -11060,7 +11060,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>52.7</v>
+        <v>52.9</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>46.9</v>
       </c>
       <c r="R39" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S39" t="n">
         <v>93.2</v>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI39" t="inlineStr">
@@ -11340,7 +11340,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>52.7</v>
+        <v>52.9</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>50.5</v>
       </c>
       <c r="R40" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S40" t="n">
         <v>93.2</v>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI40" t="inlineStr">
@@ -11872,7 +11872,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -13507,47 +13507,47 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>701807</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Carson Benge</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-24T23:05:00Z</t>
+          <t>2026-09-24T18:35:00Z</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Kumar Rocker</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>693645</t>
+          <t>677958</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -13570,65 +13570,61 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>60.8</v>
+        <v>32.3</v>
       </c>
       <c r="Q48" t="n">
-        <v>33.7</v>
+        <v>48.7</v>
       </c>
       <c r="R48" t="n">
-        <v>38.2</v>
+        <v>42.1</v>
       </c>
       <c r="S48" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T48" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U48" t="n">
-        <v>7</v>
+        <v>48.5</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr"/>
@@ -13645,134 +13641,142 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 0 HR</t>
+          <t>Contact streak: 9/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.6% barrel, 13.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.9% barrel, 17.3 HR allowed</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>13.09</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>92.54</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AQ48" t="inlineStr">
         <is>
-          <t>104.8811</t>
+          <t>99.6028</t>
         </is>
       </c>
       <c r="AR48" t="inlineStr">
         <is>
-          <t>0.4926</t>
+          <t>0.434</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr">
         <is>
-          <t>0.2271</t>
+          <t>0.157</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr">
         <is>
-          <t>0.3558</t>
+          <t>0.339</t>
         </is>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>83.78</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>45.03</t>
+          <t>33.1</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>0.2556</t>
+          <t>0.145</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>7.64</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>38.94</t>
+          <t>42.39</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
         <is>
-          <t>88.58</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="BD48" t="inlineStr">
         <is>
-          <t>0.3441</t>
+          <t>0.4392</t>
         </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
-          <t>0.1309</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="BF48" t="inlineStr">
         <is>
-          <t>26.04</t>
-        </is>
-      </c>
-      <c r="BG48" t="inlineStr"/>
-      <c r="BH48" t="inlineStr"/>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BG48" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH48" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
       <c r="BI48" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ48" t="inlineStr"/>
@@ -13783,47 +13787,47 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>673548</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seiya Suzuki</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-24T18:20:00Z</t>
+          <t>2026-09-24T23:05:00Z</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Tyler Phillips</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>663969</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -13832,7 +13836,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -13846,58 +13850,62 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>47.4</v>
+        <v>60.8</v>
       </c>
       <c r="Q49" t="n">
-        <v>39.8</v>
+        <v>33.7</v>
       </c>
       <c r="R49" t="n">
-        <v>38.8</v>
+        <v>38.2</v>
       </c>
       <c r="S49" t="n">
-        <v>100</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T49" t="n">
         <v>50</v>
       </c>
       <c r="U49" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC49" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -13917,142 +13925,134 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/31, 1 HR</t>
+          <t>Last 7 games: 4/24, 0 HR</t>
         </is>
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 14.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.6% barrel, 13.6 HR allowed</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>13.09</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>89.41</t>
+          <t>92.54</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
         <is>
-          <t>101.021</t>
+          <t>104.8811</t>
         </is>
       </c>
       <c r="AR49" t="inlineStr">
         <is>
-          <t>0.4443</t>
+          <t>0.4926</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>0.1994</t>
+          <t>0.2271</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr">
         <is>
-          <t>0.3415</t>
+          <t>0.3558</t>
         </is>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>83.78</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>40.99</t>
+          <t>45.03</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>32.11</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>0.2113</t>
+          <t>0.2556</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>7.64</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>42.77</t>
+          <t>38.94</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>89.41</t>
+          <t>88.58</t>
         </is>
       </c>
       <c r="BD49" t="inlineStr">
         <is>
-          <t>0.4015</t>
+          <t>0.3441</t>
         </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
-          <t>0.1506</t>
+          <t>0.1309</t>
         </is>
       </c>
       <c r="BF49" t="inlineStr">
         <is>
-          <t>26.01</t>
-        </is>
-      </c>
-      <c r="BG49" t="inlineStr">
-        <is>
-          <t>In From CF</t>
-        </is>
-      </c>
-      <c r="BH49" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
+          <t>26.04</t>
+        </is>
+      </c>
+      <c r="BG49" t="inlineStr"/>
+      <c r="BH49" t="inlineStr"/>
       <c r="BI49" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ49" t="inlineStr"/>
@@ -14063,47 +14063,47 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>663586</t>
+          <t>673548</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin Riley</t>
+          <t>Seiya Suzuki</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-24T23:15:00Z</t>
+          <t>2026-09-24T18:20:00Z</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Brady Singer</t>
+          <t>Tyler Phillips</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>663903</t>
+          <t>663969</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -14126,62 +14126,58 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>53.1</v>
+        <v>47.4</v>
       </c>
       <c r="Q50" t="n">
-        <v>54.8</v>
+        <v>39.8</v>
       </c>
       <c r="R50" t="n">
-        <v>30.9</v>
+        <v>38.8</v>
       </c>
       <c r="S50" t="n">
-        <v>71.7</v>
+        <v>100</v>
       </c>
       <c r="T50" t="n">
         <v>50</v>
       </c>
       <c r="U50" t="n">
-        <v>33.7</v>
+        <v>39</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14201,12 +14197,12 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -14216,12 +14212,12 @@
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 1 HR</t>
+          <t>Last 7 games: 8/31, 1 HR</t>
         </is>
       </c>
       <c r="AL50" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.9% barrel, 27.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 14.3 HR allowed</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
@@ -14231,104 +14227,112 @@
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>13.24</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>41.91</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.41</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
         <is>
-          <t>102.718</t>
+          <t>101.021</t>
         </is>
       </c>
       <c r="AR50" t="inlineStr">
         <is>
-          <t>0.4188</t>
+          <t>0.4443</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>0.1949</t>
+          <t>0.1994</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr">
         <is>
-          <t>0.3083</t>
+          <t>0.3415</t>
         </is>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>75.83</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>40.22</t>
+          <t>40.99</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>30.59</t>
+          <t>32.11</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>0.1505</t>
+          <t>0.2113</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>42.31</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>90.79</t>
+          <t>89.41</t>
         </is>
       </c>
       <c r="BD50" t="inlineStr">
         <is>
-          <t>0.4489</t>
+          <t>0.4015</t>
         </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.1506</t>
         </is>
       </c>
       <c r="BF50" t="inlineStr">
         <is>
-          <t>26.86</t>
-        </is>
-      </c>
-      <c r="BG50" t="inlineStr"/>
-      <c r="BH50" t="inlineStr"/>
+          <t>26.01</t>
+        </is>
+      </c>
+      <c r="BG50" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH50" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
       <c r="BI50" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ50" t="inlineStr"/>
@@ -14339,47 +14343,47 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>701807</t>
+          <t>663586</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Carson Benge</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-24T18:35:00Z</t>
+          <t>2026-09-24T23:15:00Z</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Kumar Rocker</t>
+          <t>Brady Singer</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>663903</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -14388,7 +14392,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -14402,61 +14406,65 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>32.3</v>
+        <v>53.1</v>
       </c>
       <c r="Q51" t="n">
-        <v>48.7</v>
+        <v>54.8</v>
       </c>
       <c r="R51" t="n">
-        <v>41.1</v>
+        <v>30.9</v>
       </c>
       <c r="S51" t="n">
-        <v>94.90000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T51" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U51" t="n">
-        <v>48.5</v>
+        <v>33.7</v>
       </c>
       <c r="V51" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr"/>
@@ -14473,12 +14481,12 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -14488,12 +14496,12 @@
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Contact streak: 9/28 over last 7 games</t>
+          <t>Last 7 games: 6/27, 1 HR</t>
         </is>
       </c>
       <c r="AL51" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.9% barrel, 17.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.9% barrel, 27.4 HR allowed</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
@@ -14503,112 +14511,104 @@
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>13.24</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ51" t="inlineStr">
         <is>
-          <t>99.6028</t>
+          <t>102.718</t>
         </is>
       </c>
       <c r="AR51" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>0.4188</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>0.1949</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>0.3083</t>
         </is>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>75.83</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>40.22</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>30.59</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>0.1505</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>42.39</t>
+          <t>42.31</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.79</t>
         </is>
       </c>
       <c r="BD51" t="inlineStr">
         <is>
-          <t>0.4392</t>
+          <t>0.4489</t>
         </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="BF51" t="inlineStr">
         <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="BG51" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH51" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t>26.86</t>
+        </is>
+      </c>
+      <c r="BG51" t="inlineStr"/>
+      <c r="BH51" t="inlineStr"/>
       <c r="BI51" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ51" t="inlineStr"/>
@@ -14619,32 +14619,32 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>699024</t>
+          <t>701538</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Leo Bernal</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-24T16:35:00Z</t>
+          <t>2026-09-25T02:10:00Z</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -14654,12 +14654,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Paul Skenes</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>694973</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -14682,61 +14682,65 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>58.6</v>
+        <v>54.3</v>
       </c>
       <c r="Q52" t="n">
+        <v>36</v>
+      </c>
+      <c r="R52" t="n">
         <v>27.6</v>
       </c>
-      <c r="R52" t="n">
-        <v>28.8</v>
-      </c>
       <c r="S52" t="n">
-        <v>86.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T52" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U52" t="n">
-        <v>40.7</v>
+        <v>36.5</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr"/>
@@ -14758,7 +14762,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -14768,127 +14772,119 @@
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 1 HR</t>
+          <t>Last 7 games: 7/29, 1 HR</t>
         </is>
       </c>
       <c r="AL52" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.7% barrel, 16.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>91.03</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>102.1888</t>
+          <t>101.2132</t>
         </is>
       </c>
       <c r="AR52" t="inlineStr">
         <is>
-          <t>0.501</t>
+          <t>0.4893</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>0.2228</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>0.3463</t>
         </is>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>72.95</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>37.63</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>0.1888</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>38.56</t>
+          <t>38.66</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>87.81</t>
+          <t>89.67</t>
         </is>
       </c>
       <c r="BD52" t="inlineStr">
         <is>
-          <t>0.3392</t>
+          <t>0.3317</t>
         </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
-          <t>0.1267</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="BF52" t="inlineStr">
         <is>
-          <t>22.94</t>
-        </is>
-      </c>
-      <c r="BG52" t="inlineStr">
-        <is>
-          <t>In From RF</t>
-        </is>
-      </c>
-      <c r="BH52" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
+          <t>28.71</t>
+        </is>
+      </c>
+      <c r="BG52" t="inlineStr"/>
+      <c r="BH52" t="inlineStr"/>
       <c r="BI52" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ52" t="inlineStr"/>
@@ -14899,32 +14895,32 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>701538</t>
+          <t>699024</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Leo Bernal</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-25T02:10:00Z</t>
+          <t>2026-09-24T16:35:00Z</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -14934,12 +14930,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Paul Skenes</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>694973</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -14948,7 +14944,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -14962,65 +14958,61 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>54.3</v>
+        <v>58.6</v>
       </c>
       <c r="Q53" t="n">
-        <v>36</v>
+        <v>27.6</v>
       </c>
       <c r="R53" t="n">
-        <v>27.6</v>
+        <v>28.8</v>
       </c>
       <c r="S53" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T53" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U53" t="n">
-        <v>36.5</v>
+        <v>39.2</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr"/>
@@ -15042,7 +15034,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
@@ -15052,119 +15044,127 @@
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/29, 1 HR</t>
+          <t>Last 7 games: 7/27, 1 HR</t>
         </is>
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.7% barrel, 16.6 HR allowed</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>91.03</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
         <is>
-          <t>101.2132</t>
+          <t>102.1888</t>
         </is>
       </c>
       <c r="AR53" t="inlineStr">
         <is>
-          <t>0.4893</t>
+          <t>0.501</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>0.2228</t>
+          <t>0.218</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr">
         <is>
-          <t>0.3463</t>
+          <t>0.355</t>
         </is>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>72.95</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>37.63</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>35.5</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>0.1888</t>
+          <t>0.185</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>38.66</t>
+          <t>38.56</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>89.67</t>
+          <t>87.81</t>
         </is>
       </c>
       <c r="BD53" t="inlineStr">
         <is>
-          <t>0.3317</t>
+          <t>0.3392</t>
         </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.1267</t>
         </is>
       </c>
       <c r="BF53" t="inlineStr">
         <is>
-          <t>28.71</t>
-        </is>
-      </c>
-      <c r="BG53" t="inlineStr"/>
-      <c r="BH53" t="inlineStr"/>
+          <t>22.94</t>
+        </is>
+      </c>
+      <c r="BG53" t="inlineStr">
+        <is>
+          <t>In From RF</t>
+        </is>
+      </c>
+      <c r="BH53" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
       <c r="BI53" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ53" t="inlineStr"/>
@@ -15451,52 +15451,52 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>663330</t>
+          <t>607043</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jahmai Jones</t>
+          <t>Brandon Nimmo</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-24T22:45:00Z</t>
+          <t>2026-09-24T18:35:00Z</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Daniel Espino</t>
+          <t>Zac Thornton</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>682982</t>
+          <t>804267</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L55" t="n">
@@ -15514,62 +15514,58 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>49.6</v>
+        <v>45.5</v>
       </c>
       <c r="Q55" t="n">
-        <v>43.5</v>
+        <v>50.5</v>
       </c>
       <c r="R55" t="n">
-        <v>28.7</v>
+        <v>42.1</v>
       </c>
       <c r="S55" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T55" t="n">
         <v>50</v>
       </c>
       <c r="U55" t="n">
-        <v>35.6</v>
+        <v>15.3</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -15589,27 +15585,27 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 1 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 13.3% barrel, 3.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.6% barrel, 13.0 HR allowed</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
@@ -15619,104 +15615,112 @@
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>46.46</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>91.97</t>
         </is>
       </c>
       <c r="AQ55" t="inlineStr">
         <is>
-          <t>102.2774</t>
+          <t>102.0213</t>
         </is>
       </c>
       <c r="AR55" t="inlineStr">
         <is>
-          <t>0.4581</t>
+          <t>0.4393</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>0.2108</t>
+          <t>0.1747</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr">
         <is>
-          <t>0.3472</t>
+          <t>0.3357</t>
         </is>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>73.39</t>
+          <t>72.34</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>50.74</t>
+          <t>33.73</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>27.92</t>
+          <t>25.77</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>0.1965</t>
+          <t>0.1544</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="BD55" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.184</t>
         </is>
       </c>
       <c r="BF55" t="inlineStr">
         <is>
-          <t>36.7</t>
-        </is>
-      </c>
-      <c r="BG55" t="inlineStr"/>
-      <c r="BH55" t="inlineStr"/>
+          <t>30.5</t>
+        </is>
+      </c>
+      <c r="BG55" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH55" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
       <c r="BI55" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ55" t="inlineStr"/>
@@ -15727,56 +15731,56 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>607043</t>
+          <t>663330</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brandon Nimmo</t>
+          <t>Jahmai Jones</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-24T18:35:00Z</t>
+          <t>2026-09-24T22:45:00Z</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Zac Thornton</t>
+          <t>Daniel Espino</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>804267</t>
+          <t>682982</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -15790,58 +15794,62 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>45.5</v>
+        <v>49.6</v>
       </c>
       <c r="Q56" t="n">
-        <v>50.5</v>
+        <v>43.5</v>
       </c>
       <c r="R56" t="n">
-        <v>41.1</v>
+        <v>28.7</v>
       </c>
       <c r="S56" t="n">
-        <v>86.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T56" t="n">
         <v>50</v>
       </c>
       <c r="U56" t="n">
-        <v>15.3</v>
+        <v>35.6</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC56" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -15861,27 +15869,27 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 4/17, 1 HR</t>
         </is>
       </c>
       <c r="AL56" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.6% barrel, 13.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 13.3% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
@@ -15891,112 +15899,104 @@
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>11.09</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>46.46</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>91.97</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
         <is>
-          <t>102.0213</t>
+          <t>102.2774</t>
         </is>
       </c>
       <c r="AR56" t="inlineStr">
         <is>
-          <t>0.4393</t>
+          <t>0.4581</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>0.1747</t>
+          <t>0.2108</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr">
         <is>
-          <t>0.3357</t>
+          <t>0.3472</t>
         </is>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>72.34</t>
+          <t>73.39</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>35.63</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>33.73</t>
+          <t>50.74</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>25.77</t>
+          <t>27.92</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>0.1544</t>
+          <t>0.1965</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="BD56" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="BF56" t="inlineStr">
         <is>
-          <t>30.5</t>
-        </is>
-      </c>
-      <c r="BG56" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH56" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t>36.7</t>
+        </is>
+      </c>
+      <c r="BG56" t="inlineStr"/>
+      <c r="BH56" t="inlineStr"/>
       <c r="BI56" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ56" t="inlineStr"/>
@@ -16917,7 +16917,7 @@
         <v>80</v>
       </c>
       <c r="U60" t="n">
-        <v>25.3</v>
+        <v>24.3</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
@@ -16984,7 +16984,7 @@
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 4/25, 1 HR</t>
         </is>
       </c>
       <c r="AL60" t="inlineStr">
@@ -17720,7 +17720,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -17744,7 +17744,7 @@
         <v>50.5</v>
       </c>
       <c r="R63" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S63" t="n">
         <v>76.2</v>
@@ -17935,7 +17935,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI63" t="inlineStr">
@@ -19940,7 +19940,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>48.7</v>
       </c>
       <c r="R71" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S71" t="n">
         <v>96.59999999999999</v>
@@ -20155,7 +20155,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI71" t="inlineStr">
@@ -21024,7 +21024,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -21856,7 +21856,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -22136,7 +22136,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -26844,7 +26844,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -29640,7 +29640,7 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
       <c r="M106" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>48.7</v>
       </c>
       <c r="R106" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S106" t="n">
         <v>64.3</v>
@@ -29855,7 +29855,7 @@
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI106" t="inlineStr">
@@ -30172,7 +30172,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -31815,52 +31815,52 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>703607</t>
+          <t>553869</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Henry Bolte</t>
+          <t>Elias Díaz</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-09-25T01:40:00Z</t>
+          <t>2026-09-24T18:35:00Z</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Peter Lambert</t>
+          <t>Zac Thornton</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>663567</t>
+          <t>804267</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L114" t="n">
@@ -31878,65 +31878,61 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P114" t="n">
-        <v>37.7</v>
+        <v>31.5</v>
       </c>
       <c r="Q114" t="n">
-        <v>32.9</v>
+        <v>50.5</v>
       </c>
       <c r="R114" t="n">
-        <v>30.9</v>
+        <v>42.1</v>
       </c>
       <c r="S114" t="n">
-        <v>88.7</v>
+        <v>52.4</v>
       </c>
       <c r="T114" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U114" t="n">
-        <v>50.3</v>
+        <v>23.7</v>
       </c>
       <c r="V114" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W114" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X114" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y114" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr"/>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD114" t="inlineStr"/>
@@ -31953,27 +31949,27 @@
       </c>
       <c r="AH114" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL114" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.8% barrel, 15.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.6% barrel, 13.0 HR allowed</t>
         </is>
       </c>
       <c r="AM114" t="inlineStr">
@@ -31983,104 +31979,112 @@
       </c>
       <c r="AN114" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>39.61</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>88.33</t>
         </is>
       </c>
       <c r="AQ114" t="inlineStr">
         <is>
-          <t>104.3571</t>
+          <t>100.5511</t>
         </is>
       </c>
       <c r="AR114" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.3445</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.1341</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>0.2666</t>
         </is>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>74.34</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>43.86</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>37.93</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>27.24</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.1515</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>35.8</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="BD114" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.184</t>
         </is>
       </c>
       <c r="BF114" t="inlineStr">
         <is>
-          <t>32.5</t>
-        </is>
-      </c>
-      <c r="BG114" t="inlineStr"/>
-      <c r="BH114" t="inlineStr"/>
+          <t>30.5</t>
+        </is>
+      </c>
+      <c r="BG114" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH114" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
       <c r="BI114" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ114" t="inlineStr"/>
@@ -32091,27 +32095,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>668939</t>
+          <t>703607</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Adley Rutschman</t>
+          <t>Henry Bolte</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-09-24T22:45:00Z</t>
+          <t>2026-09-25T01:40:00Z</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -32121,17 +32125,17 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Daniel Espino</t>
+          <t>Peter Lambert</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>682982</t>
+          <t>663567</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -32140,7 +32144,7 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>44.3</v>
+        <v>44.4</v>
       </c>
       <c r="M115" t="inlineStr">
         <is>
@@ -32154,26 +32158,26 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P115" t="n">
-        <v>31.6</v>
+        <v>37.7</v>
       </c>
       <c r="Q115" t="n">
-        <v>43.2</v>
+        <v>32.9</v>
       </c>
       <c r="R115" t="n">
-        <v>28.7</v>
+        <v>30.9</v>
       </c>
       <c r="S115" t="n">
-        <v>81.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T115" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U115" t="n">
-        <v>19.5</v>
+        <v>50.3</v>
       </c>
       <c r="V115" t="inlineStr">
         <is>
@@ -32187,7 +32191,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y115" t="inlineStr">
@@ -32212,7 +32216,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD115" t="inlineStr"/>
@@ -32229,27 +32233,27 @@
       </c>
       <c r="AH115" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/28, 0 HR</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL115" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 13.3% barrel, 3.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM115" t="inlineStr">
@@ -32259,104 +32263,104 @@
       </c>
       <c r="AN115" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AQ115" t="inlineStr">
         <is>
-          <t>99.19</t>
+          <t>104.3571</t>
         </is>
       </c>
       <c r="AR115" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr">
         <is>
-          <t>0.1606</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.318</t>
         </is>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>70.42</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>12.14</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>0.1705</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="BD115" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BE115" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="BF115" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="BG115" t="inlineStr"/>
       <c r="BH115" t="inlineStr"/>
       <c r="BI115" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ115" t="inlineStr"/>
@@ -32367,27 +32371,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>668939</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Adley Rutschman</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-09-24T23:05:00Z</t>
+          <t>2026-09-24T22:45:00Z</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -32397,17 +32401,17 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Daniel Espino</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>693645</t>
+          <t>682982</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -32430,26 +32434,26 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P116" t="n">
-        <v>41.2</v>
+        <v>31.6</v>
       </c>
       <c r="Q116" t="n">
-        <v>33.7</v>
+        <v>43.2</v>
       </c>
       <c r="R116" t="n">
-        <v>38.2</v>
+        <v>28.7</v>
       </c>
       <c r="S116" t="n">
-        <v>88.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T116" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U116" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="V116" t="inlineStr">
         <is>
@@ -32463,7 +32467,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y116" t="inlineStr">
@@ -32488,7 +32492,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD116" t="inlineStr"/>
@@ -32505,7 +32509,7 @@
       </c>
       <c r="AH116" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI116" t="inlineStr">
@@ -32520,119 +32524,119 @@
       </c>
       <c r="AK116" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/28, 0 HR</t>
+          <t>Last 7 games: 7/28, 0 HR</t>
         </is>
       </c>
       <c r="AL116" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.6% barrel, 13.6 HR allowed</t>
+          <t>switch hitter; pitcher baseline 13.3% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN116" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="AQ116" t="inlineStr">
         <is>
-          <t>103.21</t>
+          <t>99.19</t>
         </is>
       </c>
       <c r="AR116" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
         <is>
-          <t>0.1635</t>
+          <t>0.1606</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3271</t>
         </is>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>70.42</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>37.44</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>0.1624</t>
+          <t>0.1705</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>7.64</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>38.94</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>88.58</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="BD116" t="inlineStr">
         <is>
-          <t>0.3441</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
-          <t>0.1309</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="BF116" t="inlineStr">
         <is>
-          <t>26.04</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="BG116" t="inlineStr"/>
       <c r="BH116" t="inlineStr"/>
       <c r="BI116" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ116" t="inlineStr"/>
@@ -32643,27 +32647,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>641487</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>J.P. Crawford</t>
+          <t>Yandy Diaz</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-09-25T01:40:00Z</t>
+          <t>2026-09-24T23:05:00Z</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -32678,12 +32682,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>680570</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -32706,26 +32710,26 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P117" t="n">
-        <v>21.1</v>
+        <v>41.2</v>
       </c>
       <c r="Q117" t="n">
-        <v>53.6</v>
+        <v>33.7</v>
       </c>
       <c r="R117" t="n">
-        <v>25.4</v>
+        <v>38.2</v>
       </c>
       <c r="S117" t="n">
         <v>88.7</v>
       </c>
       <c r="T117" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U117" t="n">
-        <v>21.8</v>
+        <v>0</v>
       </c>
       <c r="V117" t="inlineStr">
         <is>
@@ -32764,7 +32768,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD117" t="inlineStr"/>
@@ -32781,7 +32785,7 @@
       </c>
       <c r="AH117" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI117" t="inlineStr">
@@ -32791,17 +32795,17 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/28, 1 HR</t>
+          <t>Last 7 games: 2/28, 0 HR</t>
         </is>
       </c>
       <c r="AL117" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.9% barrel, 15.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.6% barrel, 13.6 HR allowed</t>
         </is>
       </c>
       <c r="AM117" t="inlineStr">
@@ -32811,104 +32815,104 @@
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>34.49</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ117" t="inlineStr">
         <is>
-          <t>98.0324</t>
+          <t>103.21</t>
         </is>
       </c>
       <c r="AR117" t="inlineStr">
         <is>
-          <t>0.3664</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
         <is>
-          <t>0.1221</t>
+          <t>0.1635</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr">
         <is>
-          <t>0.3224</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>71.21</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>37.44</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>35.77</t>
+          <t>23.81</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>22.47</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>0.1204</t>
+          <t>0.1624</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>7.64</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>38.94</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>88.58</t>
         </is>
       </c>
       <c r="BD117" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>0.3441</t>
         </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>0.1309</t>
         </is>
       </c>
       <c r="BF117" t="inlineStr">
         <is>
-          <t>27.6</t>
+          <t>26.04</t>
         </is>
       </c>
       <c r="BG117" t="inlineStr"/>
       <c r="BH117" t="inlineStr"/>
       <c r="BI117" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ117" t="inlineStr"/>
@@ -32919,56 +32923,56 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>553869</t>
+          <t>641487</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Elias Díaz</t>
+          <t>J.P. Crawford</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-09-24T18:35:00Z</t>
+          <t>2026-09-25T01:40:00Z</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Zac Thornton</t>
+          <t>Grayson Rodriguez</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>804267</t>
+          <t>680570</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>44.2</v>
+        <v>44.3</v>
       </c>
       <c r="M118" t="inlineStr">
         <is>
@@ -32982,58 +32986,62 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P118" t="n">
-        <v>31.5</v>
+        <v>21.1</v>
       </c>
       <c r="Q118" t="n">
-        <v>50.5</v>
+        <v>53.6</v>
       </c>
       <c r="R118" t="n">
-        <v>41.1</v>
+        <v>25.4</v>
       </c>
       <c r="S118" t="n">
-        <v>52.4</v>
+        <v>88.7</v>
       </c>
       <c r="T118" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U118" t="n">
-        <v>23.7</v>
+        <v>21.8</v>
       </c>
       <c r="V118" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W118" t="inlineStr">
+      <c r="Z118" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X118" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y118" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC118" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -33053,142 +33061,134 @@
       </c>
       <c r="AH118" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 4/28, 1 HR</t>
         </is>
       </c>
       <c r="AL118" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.6% barrel, 13.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.9% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>39.61</t>
+          <t>34.49</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>88.33</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="AQ118" t="inlineStr">
         <is>
-          <t>100.5511</t>
+          <t>98.0324</t>
         </is>
       </c>
       <c r="AR118" t="inlineStr">
         <is>
-          <t>0.3445</t>
+          <t>0.3664</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr">
         <is>
-          <t>0.1341</t>
+          <t>0.1221</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr">
         <is>
-          <t>0.2666</t>
+          <t>0.3224</t>
         </is>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>74.34</t>
+          <t>71.21</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>43.86</t>
+          <t>18.53</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>37.93</t>
+          <t>35.77</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>27.24</t>
+          <t>22.47</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>0.1515</t>
+          <t>0.1204</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="BD118" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.468</t>
         </is>
       </c>
       <c r="BE118" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>0.192</t>
         </is>
       </c>
       <c r="BF118" t="inlineStr">
         <is>
-          <t>30.5</t>
-        </is>
-      </c>
-      <c r="BG118" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH118" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t>27.6</t>
+        </is>
+      </c>
+      <c r="BG118" t="inlineStr"/>
+      <c r="BH118" t="inlineStr"/>
       <c r="BI118" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ118" t="inlineStr"/>
@@ -35440,7 +35440,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -36300,7 +36300,7 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>42.5</v>
+        <v>42.7</v>
       </c>
       <c r="M130" t="inlineStr">
         <is>
@@ -36324,7 +36324,7 @@
         <v>48.7</v>
       </c>
       <c r="R130" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S130" t="n">
         <v>52.4</v>
@@ -36515,7 +36515,7 @@
       </c>
       <c r="BH130" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI130" t="inlineStr">
@@ -37108,7 +37108,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -37688,7 +37688,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="M135" t="inlineStr">
         <is>
@@ -37712,7 +37712,7 @@
         <v>48.7</v>
       </c>
       <c r="R135" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S135" t="n">
         <v>76.2</v>
@@ -37903,7 +37903,7 @@
       </c>
       <c r="BH135" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI135" t="inlineStr">
@@ -38755,32 +38755,32 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>687462</t>
+          <t>677649</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spencer Horwitz</t>
+          <t>Ezequiel Duran</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-09-24T16:35:00Z</t>
+          <t>2026-09-24T18:35:00Z</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -38790,17 +38790,17 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Kyle Leahy</t>
+          <t>Zac Thornton</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>681517</t>
+          <t>804267</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L139" t="n">
@@ -38822,22 +38822,22 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>20.9</v>
+        <v>20.4</v>
       </c>
       <c r="Q139" t="n">
-        <v>51.3</v>
+        <v>50.5</v>
       </c>
       <c r="R139" t="n">
-        <v>28.8</v>
+        <v>42.1</v>
       </c>
       <c r="S139" t="n">
         <v>64.3</v>
       </c>
       <c r="T139" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U139" t="n">
-        <v>28.9</v>
+        <v>0</v>
       </c>
       <c r="V139" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
       <c r="AB139" t="inlineStr"/>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD139" t="inlineStr"/>
@@ -38889,12 +38889,12 @@
       </c>
       <c r="AH139" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ139" t="inlineStr">
@@ -38904,127 +38904,127 @@
       </c>
       <c r="AK139" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/16, 0 HR</t>
+          <t>Last 7 games: 2/26, 0 HR</t>
         </is>
       </c>
       <c r="AL139" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.7% barrel, 12.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.6% barrel, 13.0 HR allowed</t>
         </is>
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN139" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>86.98</t>
+          <t>87.82</t>
         </is>
       </c>
       <c r="AQ139" t="inlineStr">
         <is>
-          <t>97.4124</t>
+          <t>98.9997</t>
         </is>
       </c>
       <c r="AR139" t="inlineStr">
         <is>
-          <t>0.3685</t>
+          <t>0.3496</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr">
         <is>
-          <t>0.1318</t>
+          <t>0.1146</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr">
         <is>
-          <t>0.3183</t>
+          <t>0.2862</t>
         </is>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>68.54</t>
+          <t>72.27</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>24.59</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>39.52</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>27.63</t>
+          <t>21.58</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>0.1333</t>
+          <t>0.1355</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>46.13</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="BD139" t="inlineStr">
         <is>
-          <t>0.4363</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BE139" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.184</t>
         </is>
       </c>
       <c r="BF139" t="inlineStr">
         <is>
-          <t>23.17</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="BG139" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH139" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI139" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ139" t="inlineStr"/>
@@ -39084,7 +39084,7 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="M140" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>75</v>
       </c>
       <c r="U140" t="n">
-        <v>24</v>
+        <v>22.8</v>
       </c>
       <c r="V140" t="inlineStr">
         <is>
@@ -39174,7 +39174,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ140" t="inlineStr">
@@ -39184,7 +39184,7 @@
       </c>
       <c r="AK140" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 1 HR</t>
+          <t>Last 7 games: 3/20, 1 HR</t>
         </is>
       </c>
       <c r="AL140" t="inlineStr">
@@ -39315,32 +39315,32 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>677649</t>
+          <t>687462</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Ezequiel Duran</t>
+          <t>Spencer Horwitz</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-09-24T18:35:00Z</t>
+          <t>2026-09-24T16:35:00Z</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -39350,21 +39350,21 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Zac Thornton</t>
+          <t>Kyle Leahy</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>804267</t>
+          <t>681517</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="M141" t="inlineStr">
         <is>
@@ -39382,22 +39382,22 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>20.4</v>
+        <v>20.9</v>
       </c>
       <c r="Q141" t="n">
-        <v>50.5</v>
+        <v>51.3</v>
       </c>
       <c r="R141" t="n">
-        <v>41.1</v>
+        <v>28.8</v>
       </c>
       <c r="S141" t="n">
         <v>64.3</v>
       </c>
       <c r="T141" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U141" t="n">
-        <v>0</v>
+        <v>26.1</v>
       </c>
       <c r="V141" t="inlineStr">
         <is>
@@ -39432,7 +39432,7 @@
       <c r="AB141" t="inlineStr"/>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD141" t="inlineStr"/>
@@ -39449,12 +39449,12 @@
       </c>
       <c r="AH141" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ141" t="inlineStr">
@@ -39464,127 +39464,127 @@
       </c>
       <c r="AK141" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/26, 0 HR</t>
+          <t>Last 7 games: 5/17, 0 HR</t>
         </is>
       </c>
       <c r="AL141" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.6% barrel, 13.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.7% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN141" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>32.36</t>
         </is>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>87.82</t>
+          <t>86.98</t>
         </is>
       </c>
       <c r="AQ141" t="inlineStr">
         <is>
-          <t>98.9997</t>
+          <t>97.4124</t>
         </is>
       </c>
       <c r="AR141" t="inlineStr">
         <is>
-          <t>0.3496</t>
+          <t>0.3685</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr">
         <is>
-          <t>0.1146</t>
+          <t>0.1318</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr">
         <is>
-          <t>0.2862</t>
+          <t>0.3183</t>
         </is>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>72.27</t>
+          <t>68.54</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>24.59</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>35.45</t>
+          <t>39.52</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>27.63</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>0.1355</t>
+          <t>0.1333</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>46.13</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="BD141" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.4363</t>
         </is>
       </c>
       <c r="BE141" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="BF141" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>23.17</t>
         </is>
       </c>
       <c r="BG141" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH141" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI141" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ141" t="inlineStr"/>
@@ -41535,27 +41535,27 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>664983</t>
+          <t>643376</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Jake McCarthy</t>
+          <t>Danny Jansen</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-09-24T19:10:00Z</t>
+          <t>2026-09-24T18:35:00Z</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -41565,17 +41565,17 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Eduardo Rodriguez</t>
+          <t>Zac Thornton</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>593958</t>
+          <t>804267</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -41598,26 +41598,26 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P149" t="n">
-        <v>16.7</v>
+        <v>22.6</v>
       </c>
       <c r="Q149" t="n">
-        <v>37.8</v>
+        <v>50.5</v>
       </c>
       <c r="R149" t="n">
-        <v>48.7</v>
+        <v>42.1</v>
       </c>
       <c r="S149" t="n">
-        <v>93.2</v>
+        <v>44.8</v>
       </c>
       <c r="T149" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U149" t="n">
-        <v>19.5</v>
+        <v>23.7</v>
       </c>
       <c r="V149" t="inlineStr">
         <is>
@@ -41631,7 +41631,7 @@
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y149" t="inlineStr">
@@ -41652,7 +41652,7 @@
       <c r="AB149" t="inlineStr"/>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD149" t="inlineStr"/>
@@ -41669,12 +41669,12 @@
       </c>
       <c r="AH149" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ149" t="inlineStr">
@@ -41684,127 +41684,127 @@
       </c>
       <c r="AK149" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/28, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL149" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 20.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.6% barrel, 13.0 HR allowed</t>
         </is>
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN149" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>28.16</t>
+          <t>35.01</t>
         </is>
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>85.05</t>
+          <t>87.67</t>
         </is>
       </c>
       <c r="AQ149" t="inlineStr">
         <is>
-          <t>96.8804</t>
+          <t>97.8804</t>
         </is>
       </c>
       <c r="AR149" t="inlineStr">
         <is>
-          <t>0.4034</t>
+          <t>0.3192</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr">
         <is>
-          <t>0.1378</t>
+          <t>0.129</t>
         </is>
       </c>
       <c r="AT149" t="inlineStr">
         <is>
-          <t>0.3133</t>
+          <t>0.2776</t>
         </is>
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>70.89</t>
+          <t>69.85</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>37.87</t>
+          <t>54.05</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>28.84</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>0.1746</t>
+          <t>0.1658</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>33.66</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>87.57</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="BD149" t="inlineStr">
         <is>
-          <t>0.4181</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BE149" t="inlineStr">
         <is>
-          <t>0.1657</t>
+          <t>0.184</t>
         </is>
       </c>
       <c r="BF149" t="inlineStr">
         <is>
-          <t>27.26</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="BG149" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH149" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI149" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ149" t="inlineStr"/>
@@ -41815,56 +41815,56 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>664983</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Jake McCarthy</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-09-25T02:10:00Z</t>
+          <t>2026-09-24T19:10:00Z</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Eduardo Rodriguez</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>601713</t>
+          <t>593958</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>40.3</v>
+        <v>40.4</v>
       </c>
       <c r="M150" t="inlineStr">
         <is>
@@ -41878,62 +41878,58 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P150" t="n">
-        <v>35.4</v>
+        <v>16.7</v>
       </c>
       <c r="Q150" t="n">
-        <v>43.6</v>
+        <v>37.8</v>
       </c>
       <c r="R150" t="n">
-        <v>27.6</v>
+        <v>48.7</v>
       </c>
       <c r="S150" t="n">
-        <v>47.9</v>
+        <v>93.2</v>
       </c>
       <c r="T150" t="n">
         <v>50</v>
       </c>
       <c r="U150" t="n">
-        <v>56.6</v>
+        <v>19.5</v>
       </c>
       <c r="V150" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W150" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X150" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y150" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr"/>
       <c r="AC150" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -41953,134 +41949,142 @@
       </c>
       <c r="AH150" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
         <is>
-          <t>Contact streak: 9/24 over last 7 games</t>
+          <t>Last 7 games: 7/28, 0 HR</t>
         </is>
       </c>
       <c r="AL150" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.6% barrel, 8.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 20.1 HR allowed</t>
         </is>
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN150" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>28.16</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>88.67</t>
+          <t>85.05</t>
         </is>
       </c>
       <c r="AQ150" t="inlineStr">
         <is>
-          <t>99.6698</t>
+          <t>96.8804</t>
         </is>
       </c>
       <c r="AR150" t="inlineStr">
         <is>
-          <t>0.4357</t>
+          <t>0.4034</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr">
         <is>
-          <t>0.1665</t>
+          <t>0.1378</t>
         </is>
       </c>
       <c r="AT150" t="inlineStr">
         <is>
-          <t>0.3342</t>
+          <t>0.3133</t>
         </is>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>72.85</t>
+          <t>70.89</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>38.39</t>
+          <t>37.87</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>28.51</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>0.1869</t>
+          <t>0.1746</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>7.71</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>38.63</t>
+          <t>33.66</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>89.46</t>
+          <t>87.57</t>
         </is>
       </c>
       <c r="BD150" t="inlineStr">
         <is>
-          <t>0.3722</t>
+          <t>0.4181</t>
         </is>
       </c>
       <c r="BE150" t="inlineStr">
         <is>
-          <t>0.1568</t>
+          <t>0.1657</t>
         </is>
       </c>
       <c r="BF150" t="inlineStr">
         <is>
-          <t>33.3</t>
-        </is>
-      </c>
-      <c r="BG150" t="inlineStr"/>
-      <c r="BH150" t="inlineStr"/>
+          <t>27.26</t>
+        </is>
+      </c>
+      <c r="BG150" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH150" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI150" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ150" t="inlineStr"/>
@@ -42091,56 +42095,56 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>640459</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Brian Navarreto</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-09-24T18:20:00Z</t>
+          <t>2026-09-25T02:10:00Z</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Matthew Boyd</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>571510</t>
+          <t>601713</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
       <c r="M151" t="inlineStr">
         <is>
@@ -42154,58 +42158,62 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P151" t="n">
-        <v>28.9</v>
+        <v>35.4</v>
       </c>
       <c r="Q151" t="n">
-        <v>41.3</v>
+        <v>43.6</v>
       </c>
       <c r="R151" t="n">
-        <v>38.8</v>
+        <v>27.6</v>
       </c>
       <c r="S151" t="n">
-        <v>44.8</v>
+        <v>47.9</v>
       </c>
       <c r="T151" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U151" t="n">
-        <v>32</v>
+        <v>56.6</v>
       </c>
       <c r="V151" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W151" t="inlineStr">
+      <c r="Z151" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X151" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y151" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB151" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC151" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -42225,142 +42233,134 @@
       </c>
       <c r="AH151" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI151" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ151" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>Contact streak: 1/3 over last 7 games</t>
+          <t>Contact streak: 9/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL151" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 16.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.6% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN151" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>88.12</t>
+          <t>88.67</t>
         </is>
       </c>
       <c r="AQ151" t="inlineStr">
         <is>
-          <t>98.2729</t>
+          <t>99.6698</t>
         </is>
       </c>
       <c r="AR151" t="inlineStr">
         <is>
-          <t>0.2713</t>
+          <t>0.4357</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr">
         <is>
-          <t>0.1092</t>
+          <t>0.1665</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr">
         <is>
-          <t>0.2213</t>
+          <t>0.3342</t>
         </is>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>72.86</t>
+          <t>72.85</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>22.82</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>38.39</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>20.91</t>
+          <t>28.51</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>0.1813</t>
+          <t>0.1869</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>38.14</t>
+          <t>38.63</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>88.43</t>
+          <t>89.46</t>
         </is>
       </c>
       <c r="BD151" t="inlineStr">
         <is>
-          <t>0.4176</t>
+          <t>0.3722</t>
         </is>
       </c>
       <c r="BE151" t="inlineStr">
         <is>
-          <t>0.1601</t>
+          <t>0.1568</t>
         </is>
       </c>
       <c r="BF151" t="inlineStr">
         <is>
-          <t>26.2</t>
-        </is>
-      </c>
-      <c r="BG151" t="inlineStr">
-        <is>
-          <t>In From CF</t>
-        </is>
-      </c>
-      <c r="BH151" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
+          <t>33.3</t>
+        </is>
+      </c>
+      <c r="BG151" t="inlineStr"/>
+      <c r="BH151" t="inlineStr"/>
       <c r="BI151" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ151" t="inlineStr"/>
@@ -42371,27 +42371,27 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>643376</t>
+          <t>640459</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Danny Jansen</t>
+          <t>Brian Navarreto</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-09-24T18:35:00Z</t>
+          <t>2026-09-24T18:20:00Z</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -42406,12 +42406,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Zac Thornton</t>
+          <t>Matthew Boyd</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>804267</t>
+          <t>571510</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -42434,17 +42434,17 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P152" t="n">
-        <v>22.6</v>
+        <v>28.9</v>
       </c>
       <c r="Q152" t="n">
-        <v>50.5</v>
+        <v>41.3</v>
       </c>
       <c r="R152" t="n">
-        <v>41.1</v>
+        <v>38.8</v>
       </c>
       <c r="S152" t="n">
         <v>44.8</v>
@@ -42453,7 +42453,7 @@
         <v>78</v>
       </c>
       <c r="U152" t="n">
-        <v>23.7</v>
+        <v>32</v>
       </c>
       <c r="V152" t="inlineStr">
         <is>
@@ -42488,7 +42488,7 @@
       <c r="AB152" t="inlineStr"/>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD152" t="inlineStr"/>
@@ -42505,12 +42505,12 @@
       </c>
       <c r="AH152" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AJ152" t="inlineStr">
@@ -42520,127 +42520,127 @@
       </c>
       <c r="AK152" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Contact streak: 1/3 over last 7 games</t>
         </is>
       </c>
       <c r="AL152" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.6% barrel, 13.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 16.2 HR allowed</t>
         </is>
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>35.01</t>
+          <t>35.34</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>87.67</t>
+          <t>88.12</t>
         </is>
       </c>
       <c r="AQ152" t="inlineStr">
         <is>
-          <t>97.8804</t>
+          <t>98.2729</t>
         </is>
       </c>
       <c r="AR152" t="inlineStr">
         <is>
-          <t>0.3192</t>
+          <t>0.2713</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>0.1092</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr">
         <is>
-          <t>0.2776</t>
+          <t>0.2213</t>
         </is>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>69.85</t>
+          <t>72.86</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>22.82</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>54.05</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>28.84</t>
+          <t>20.91</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>0.1658</t>
+          <t>0.1813</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>38.14</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.43</t>
         </is>
       </c>
       <c r="BD152" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.4176</t>
         </is>
       </c>
       <c r="BE152" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>0.1601</t>
         </is>
       </c>
       <c r="BF152" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BG152" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH152" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>66</t>
         </is>
       </c>
       <c r="BI152" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ152" t="inlineStr"/>
@@ -47112,7 +47112,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -47668,7 +47668,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -48224,7 +48224,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -48898,7 +48898,7 @@
       </c>
       <c r="AI175" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ175" t="inlineStr">
@@ -48908,7 +48908,7 @@
       </c>
       <c r="AK175" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/22, 0 HR</t>
+          <t>Last 7 games: 2/23, 0 HR</t>
         </is>
       </c>
       <c r="AL175" t="inlineStr">
@@ -49620,7 +49620,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -50427,47 +50427,47 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>699302</t>
+          <t>703492</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Hector Rodriguez</t>
+          <t>Nick Morabito</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-09-24T23:15:00Z</t>
+          <t>2026-09-24T18:35:00Z</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Tyler Mahle</t>
+          <t>Kumar Rocker</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>641816</t>
+          <t>677958</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -50490,62 +50490,58 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P181" t="n">
-        <v>21.7</v>
+        <v>20</v>
       </c>
       <c r="Q181" t="n">
-        <v>35.8</v>
+        <v>48.7</v>
       </c>
       <c r="R181" t="n">
-        <v>30.9</v>
+        <v>42.1</v>
       </c>
       <c r="S181" t="n">
-        <v>59.8</v>
+        <v>44.8</v>
       </c>
       <c r="T181" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U181" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V181" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W181" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X181" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y181" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z181" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr"/>
       <c r="AC181" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -50565,12 +50561,12 @@
       </c>
       <c r="AH181" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI181" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ181" t="inlineStr">
@@ -50580,12 +50576,12 @@
       </c>
       <c r="AK181" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/22, 0 HR</t>
+          <t>Last 7 games: 3/15, 0 HR</t>
         </is>
       </c>
       <c r="AL181" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 14.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.9% barrel, 17.3 HR allowed</t>
         </is>
       </c>
       <c r="AM181" t="inlineStr">
@@ -50595,104 +50591,112 @@
       </c>
       <c r="AN181" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AQ181" t="inlineStr">
         <is>
-          <t>98.5539</t>
+          <t>100.2027</t>
         </is>
       </c>
       <c r="AR181" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>0.319</t>
         </is>
       </c>
       <c r="AS181" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AT181" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>0.027</t>
         </is>
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>37.31</t>
+          <t>42.39</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
         <is>
-          <t>89.27</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="BD181" t="inlineStr">
         <is>
-          <t>0.3941</t>
+          <t>0.4392</t>
         </is>
       </c>
       <c r="BE181" t="inlineStr">
         <is>
-          <t>0.1467</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="BF181" t="inlineStr">
         <is>
-          <t>26.7</t>
-        </is>
-      </c>
-      <c r="BG181" t="inlineStr"/>
-      <c r="BH181" t="inlineStr"/>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BG181" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH181" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
       <c r="BI181" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ181" t="inlineStr"/>
@@ -50703,47 +50707,47 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>703492</t>
+          <t>699302</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Nick Morabito</t>
+          <t>Hector Rodriguez</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-09-24T18:35:00Z</t>
+          <t>2026-09-24T23:15:00Z</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Kumar Rocker</t>
+          <t>Tyler Mahle</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>641816</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -50752,72 +50756,76 @@
         </is>
       </c>
       <c r="L182" t="n">
+        <v>36</v>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>Watch List</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>Projected Lineup, Platoon Edge</t>
+        </is>
+      </c>
+      <c r="P182" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="Q182" t="n">
         <v>35.8</v>
       </c>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>Longshot</t>
-        </is>
-      </c>
-      <c r="N182" t="inlineStr">
-        <is>
-          <t>Watch List</t>
-        </is>
-      </c>
-      <c r="O182" t="inlineStr">
-        <is>
-          <t>No major boost</t>
-        </is>
-      </c>
-      <c r="P182" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q182" t="n">
-        <v>48.7</v>
-      </c>
       <c r="R182" t="n">
-        <v>41.1</v>
+        <v>30.9</v>
       </c>
       <c r="S182" t="n">
-        <v>44.8</v>
+        <v>59.8</v>
       </c>
       <c r="T182" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U182" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="V182" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W182" t="inlineStr">
+      <c r="Z182" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X182" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y182" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z182" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB182" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC182" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -50837,12 +50845,12 @@
       </c>
       <c r="AH182" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI182" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ182" t="inlineStr">
@@ -50852,12 +50860,12 @@
       </c>
       <c r="AK182" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/15, 0 HR</t>
+          <t>Last 7 games: 1/22, 0 HR</t>
         </is>
       </c>
       <c r="AL182" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.9% barrel, 17.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 14.1 HR allowed</t>
         </is>
       </c>
       <c r="AM182" t="inlineStr">
@@ -50867,112 +50875,104 @@
       </c>
       <c r="AN182" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AQ182" t="inlineStr">
         <is>
-          <t>100.2027</t>
+          <t>98.5539</t>
         </is>
       </c>
       <c r="AR182" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>0.308</t>
         </is>
       </c>
       <c r="AS182" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.114</t>
         </is>
       </c>
       <c r="AT182" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.245</t>
         </is>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>0.156</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>42.39</t>
+          <t>37.31</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.27</t>
         </is>
       </c>
       <c r="BD182" t="inlineStr">
         <is>
-          <t>0.4392</t>
+          <t>0.3941</t>
         </is>
       </c>
       <c r="BE182" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.1467</t>
         </is>
       </c>
       <c r="BF182" t="inlineStr">
         <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="BG182" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH182" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="BG182" t="inlineStr"/>
+      <c r="BH182" t="inlineStr"/>
       <c r="BI182" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ182" t="inlineStr"/>
@@ -54072,7 +54072,7 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>34.2</v>
+        <v>34.1</v>
       </c>
       <c r="M194" t="inlineStr">
         <is>
@@ -54105,7 +54105,7 @@
         <v>75</v>
       </c>
       <c r="U194" t="n">
-        <v>28.9</v>
+        <v>27.6</v>
       </c>
       <c r="V194" t="inlineStr">
         <is>
@@ -54162,7 +54162,7 @@
       </c>
       <c r="AI194" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ194" t="inlineStr">
@@ -54172,7 +54172,7 @@
       </c>
       <c r="AK194" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 4/22, 1 HR</t>
         </is>
       </c>
       <c r="AL194" t="inlineStr">
@@ -54608,7 +54608,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -57096,7 +57096,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -61326,7 +61326,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>65.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -61350,7 +61350,7 @@
         <v>48.7</v>
       </c>
       <c r="R3" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -61541,7 +61541,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -61858,7 +61858,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -65490,7 +65490,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>57.5</v>
+        <v>57.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -65514,7 +65514,7 @@
         <v>50.5</v>
       </c>
       <c r="R18" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S18" t="n">
         <v>94.90000000000001</v>
@@ -65705,7 +65705,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -65770,7 +65770,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>56.8</v>
+        <v>57</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -65794,7 +65794,7 @@
         <v>50.5</v>
       </c>
       <c r="R19" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S19" t="n">
         <v>100</v>
@@ -65985,7 +65985,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-09-24_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-09-24_full.xlsx
@@ -36143,24 +36143,24 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>686681</t>
+          <t>803011</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Michael Massey</t>
+          <t>Sam Antonacci</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F129" t="inlineStr">
         <is>
           <t>2026-09-24T18:10:00Z</t>
@@ -36173,17 +36173,17 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>David Sandlin</t>
+          <t>Randy Dobnak</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>689818</t>
+          <t>677976</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -36192,7 +36192,7 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="M129" t="inlineStr">
         <is>
@@ -36206,26 +36206,26 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P129" t="n">
-        <v>26.8</v>
+        <v>19</v>
       </c>
       <c r="Q129" t="n">
-        <v>31.5</v>
+        <v>36.3</v>
       </c>
       <c r="R129" t="n">
         <v>30.2</v>
       </c>
       <c r="S129" t="n">
-        <v>86.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T129" t="n">
         <v>80</v>
       </c>
       <c r="U129" t="n">
-        <v>23.4</v>
+        <v>29.7</v>
       </c>
       <c r="V129" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y129" t="inlineStr">
@@ -36260,7 +36260,7 @@
       <c r="AB129" t="inlineStr"/>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD129" t="inlineStr"/>
@@ -36277,27 +36277,27 @@
       </c>
       <c r="AH129" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 1 HR</t>
+          <t>Last 7 games: 7/22, 0 HR</t>
         </is>
       </c>
       <c r="AL129" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 6.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 5.2 HR allowed</t>
         </is>
       </c>
       <c r="AM129" t="inlineStr">
@@ -36307,97 +36307,97 @@
       </c>
       <c r="AN129" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>37.41</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>88.83</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AQ129" t="inlineStr">
         <is>
-          <t>98.6155</t>
+          <t>97.5328</t>
         </is>
       </c>
       <c r="AR129" t="inlineStr">
         <is>
-          <t>0.3908</t>
+          <t>0.393</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr">
         <is>
-          <t>0.1395</t>
+          <t>0.116</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr">
         <is>
-          <t>0.2937</t>
+          <t>0.343</t>
         </is>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>71.36</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>49.01</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>0.1334</t>
+          <t>0.121</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>44.68</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>91.39</t>
         </is>
       </c>
       <c r="BD129" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.422</t>
         </is>
       </c>
       <c r="BE129" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>0.138</t>
         </is>
       </c>
       <c r="BF129" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>23.18</t>
         </is>
       </c>
       <c r="BG129" t="inlineStr">
@@ -36423,24 +36423,24 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>803011</t>
+          <t>686681</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Sam Antonacci</t>
+          <t>Michael Massey</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
       <c r="F130" t="inlineStr">
         <is>
           <t>2026-09-24T18:10:00Z</t>
@@ -36453,17 +36453,17 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Randy Dobnak</t>
+          <t>David Sandlin</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>677976</t>
+          <t>689818</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -36486,26 +36486,26 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P130" t="n">
-        <v>19</v>
+        <v>26.8</v>
       </c>
       <c r="Q130" t="n">
-        <v>36.3</v>
+        <v>31.5</v>
       </c>
       <c r="R130" t="n">
         <v>30.2</v>
       </c>
       <c r="S130" t="n">
-        <v>93.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T130" t="n">
         <v>80</v>
       </c>
       <c r="U130" t="n">
-        <v>29.7</v>
+        <v>22.6</v>
       </c>
       <c r="V130" t="inlineStr">
         <is>
@@ -36519,7 +36519,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y130" t="inlineStr">
@@ -36540,7 +36540,7 @@
       <c r="AB130" t="inlineStr"/>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD130" t="inlineStr"/>
@@ -36557,27 +36557,27 @@
       </c>
       <c r="AH130" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/22, 0 HR</t>
+          <t>Last 7 games: 4/27, 1 HR</t>
         </is>
       </c>
       <c r="AL130" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 5.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM130" t="inlineStr">
@@ -36587,97 +36587,97 @@
       </c>
       <c r="AN130" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>37.41</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.83</t>
         </is>
       </c>
       <c r="AQ130" t="inlineStr">
         <is>
-          <t>97.5328</t>
+          <t>98.6155</t>
         </is>
       </c>
       <c r="AR130" t="inlineStr">
         <is>
-          <t>0.393</t>
+          <t>0.3908</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>0.1395</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>0.2937</t>
         </is>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>71.36</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>49.01</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>0.1334</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>44.68</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>91.39</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="BD130" t="inlineStr">
         <is>
-          <t>0.422</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BE130" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>0.153</t>
         </is>
       </c>
       <c r="BF130" t="inlineStr">
         <is>
-          <t>23.18</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="BG130" t="inlineStr">
@@ -37543,27 +37543,27 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>621020</t>
+          <t>670231</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Dansby Swanson</t>
+          <t>John Rave</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-09-24T18:20:00Z</t>
+          <t>2026-09-24T18:10:00Z</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -37573,17 +37573,17 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Tyler Phillips</t>
+          <t>David Sandlin</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>663969</t>
+          <t>689818</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -37592,7 +37592,7 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="M134" t="inlineStr">
         <is>
@@ -37606,26 +37606,26 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P134" t="n">
-        <v>38.8</v>
+        <v>31.6</v>
       </c>
       <c r="Q134" t="n">
-        <v>39.8</v>
+        <v>31.5</v>
       </c>
       <c r="R134" t="n">
-        <v>38.3</v>
+        <v>30.2</v>
       </c>
       <c r="S134" t="n">
-        <v>44.8</v>
+        <v>64.3</v>
       </c>
       <c r="T134" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U134" t="n">
-        <v>37.8</v>
+        <v>44.1</v>
       </c>
       <c r="V134" t="inlineStr">
         <is>
@@ -37639,7 +37639,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y134" t="inlineStr">
@@ -37660,7 +37660,7 @@
       <c r="AB134" t="inlineStr"/>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD134" t="inlineStr"/>
@@ -37677,12 +37677,12 @@
       </c>
       <c r="AH134" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ134" t="inlineStr">
@@ -37692,12 +37692,12 @@
       </c>
       <c r="AK134" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 1 HR</t>
+          <t>Last 7 games: 7/24, 1 HR</t>
         </is>
       </c>
       <c r="AL134" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 14.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM134" t="inlineStr">
@@ -37707,112 +37707,112 @@
       </c>
       <c r="AN134" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>37.97</t>
         </is>
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="AQ134" t="inlineStr">
         <is>
-          <t>99.9731</t>
+          <t>100.0593</t>
         </is>
       </c>
       <c r="AR134" t="inlineStr">
         <is>
-          <t>0.4133</t>
+          <t>0.3735</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr">
         <is>
-          <t>0.1778</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.3083</t>
         </is>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>71.32</t>
+          <t>73.97</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>38.53</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>29.26</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>0.1842</t>
+          <t>0.1775</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>42.77</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>89.41</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="BD134" t="inlineStr">
         <is>
-          <t>0.4015</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BE134" t="inlineStr">
         <is>
-          <t>0.1506</t>
+          <t>0.153</t>
         </is>
       </c>
       <c r="BF134" t="inlineStr">
         <is>
-          <t>26.01</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="BG134" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH134" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI134" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ134" t="inlineStr"/>
@@ -38103,27 +38103,27 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>670231</t>
+          <t>621020</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>John Rave</t>
+          <t>Dansby Swanson</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-09-24T18:10:00Z</t>
+          <t>2026-09-24T18:20:00Z</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -38133,17 +38133,17 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>David Sandlin</t>
+          <t>Tyler Phillips</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>689818</t>
+          <t>663969</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -38166,26 +38166,26 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P136" t="n">
-        <v>31.6</v>
+        <v>38.8</v>
       </c>
       <c r="Q136" t="n">
-        <v>31.5</v>
+        <v>39.8</v>
       </c>
       <c r="R136" t="n">
-        <v>30.2</v>
+        <v>38.3</v>
       </c>
       <c r="S136" t="n">
-        <v>64.3</v>
+        <v>44.8</v>
       </c>
       <c r="T136" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U136" t="n">
-        <v>39.5</v>
+        <v>36</v>
       </c>
       <c r="V136" t="inlineStr">
         <is>
@@ -38199,7 +38199,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y136" t="inlineStr">
@@ -38220,7 +38220,7 @@
       <c r="AB136" t="inlineStr"/>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD136" t="inlineStr"/>
@@ -38237,12 +38237,12 @@
       </c>
       <c r="AH136" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ136" t="inlineStr">
@@ -38252,12 +38252,12 @@
       </c>
       <c r="AK136" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 1 HR</t>
+          <t>Last 7 games: 5/21, 1 HR</t>
         </is>
       </c>
       <c r="AL136" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 6.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 14.3 HR allowed</t>
         </is>
       </c>
       <c r="AM136" t="inlineStr">
@@ -38267,112 +38267,112 @@
       </c>
       <c r="AN136" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>37.97</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AQ136" t="inlineStr">
         <is>
-          <t>100.0593</t>
+          <t>99.9731</t>
         </is>
       </c>
       <c r="AR136" t="inlineStr">
         <is>
-          <t>0.3735</t>
+          <t>0.4133</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>0.1778</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr">
         <is>
-          <t>0.3083</t>
+          <t>0.317</t>
         </is>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>73.97</t>
+          <t>71.32</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>29.26</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>0.1775</t>
+          <t>0.1842</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>89.41</t>
         </is>
       </c>
       <c r="BD136" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.4015</t>
         </is>
       </c>
       <c r="BE136" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>0.1506</t>
         </is>
       </c>
       <c r="BF136" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>26.01</t>
         </is>
       </c>
       <c r="BG136" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH136" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>65</t>
         </is>
       </c>
       <c r="BI136" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ136" t="inlineStr"/>
@@ -48423,56 +48423,56 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>679845</t>
+          <t>676609</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Nick Loftin</t>
+          <t>José Caballero</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-09-24T18:10:00Z</t>
+          <t>2026-09-24T23:05:00Z</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>David Sandlin</t>
+          <t>Ian Seymour</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>689818</t>
+          <t>693855</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L173" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="M173" t="inlineStr">
         <is>
@@ -48486,26 +48486,26 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P173" t="n">
-        <v>16.5</v>
+        <v>9.4</v>
       </c>
       <c r="Q173" t="n">
-        <v>31.5</v>
+        <v>44.8</v>
       </c>
       <c r="R173" t="n">
-        <v>30.2</v>
+        <v>50.2</v>
       </c>
       <c r="S173" t="n">
-        <v>76.2</v>
+        <v>44.8</v>
       </c>
       <c r="T173" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U173" t="n">
-        <v>57.5</v>
+        <v>17.3</v>
       </c>
       <c r="V173" t="inlineStr">
         <is>
@@ -48519,7 +48519,7 @@
       </c>
       <c r="X173" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y173" t="inlineStr">
@@ -48540,7 +48540,7 @@
       <c r="AB173" t="inlineStr"/>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD173" t="inlineStr"/>
@@ -48557,27 +48557,27 @@
       </c>
       <c r="AH173" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI173" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
         <is>
-          <t>Contact streak: 8/21 over last 7 games</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL173" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 6.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.4% barrel, 19.0 HR allowed</t>
         </is>
       </c>
       <c r="AM173" t="inlineStr">
@@ -48587,112 +48587,112 @@
       </c>
       <c r="AN173" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>30.92</t>
+          <t>27.24</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>87.22</t>
+          <t>84.53</t>
         </is>
       </c>
       <c r="AQ173" t="inlineStr">
         <is>
-          <t>97.0725</t>
+          <t>96.4163</t>
         </is>
       </c>
       <c r="AR173" t="inlineStr">
         <is>
-          <t>0.3443</t>
+          <t>0.3362</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr">
         <is>
-          <t>0.1144</t>
+          <t>0.1101</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr">
         <is>
-          <t>0.294</t>
+          <t>0.2855</t>
         </is>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>68.98</t>
+          <t>68.96</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>43.17</t>
+          <t>41.74</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>28.22</t>
+          <t>21.31</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>0.1476</t>
+          <t>0.1278</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>88.42</t>
         </is>
       </c>
       <c r="BD173" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.3966</t>
         </is>
       </c>
       <c r="BE173" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>0.1705</t>
         </is>
       </c>
       <c r="BF173" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="BG173" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH173" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI173" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ173" t="inlineStr"/>
@@ -48703,32 +48703,32 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>676609</t>
+          <t>669242</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>José Caballero</t>
+          <t>Tommy Edman</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-09-24T23:05:00Z</t>
+          <t>2026-09-25T02:10:00Z</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -48738,17 +48738,17 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Ian Seymour</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>693855</t>
+          <t>601713</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L174" t="n">
@@ -48766,58 +48766,62 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P174" t="n">
-        <v>9.4</v>
+        <v>20.8</v>
       </c>
       <c r="Q174" t="n">
-        <v>44.8</v>
+        <v>42.7</v>
       </c>
       <c r="R174" t="n">
-        <v>50.2</v>
+        <v>27.6</v>
       </c>
       <c r="S174" t="n">
-        <v>44.8</v>
+        <v>40.2</v>
       </c>
       <c r="T174" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U174" t="n">
-        <v>17.3</v>
+        <v>37.4</v>
       </c>
       <c r="V174" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X174" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W174" t="inlineStr">
+      <c r="Z174" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X174" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y174" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z174" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB174" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB174" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC174" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -48837,142 +48841,134 @@
       </c>
       <c r="AH174" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI174" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL174" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.4% barrel, 19.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.6% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN174" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>27.24</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>84.53</t>
+          <t>87.67</t>
         </is>
       </c>
       <c r="AQ174" t="inlineStr">
         <is>
-          <t>96.4163</t>
+          <t>98.774</t>
         </is>
       </c>
       <c r="AR174" t="inlineStr">
         <is>
-          <t>0.3362</t>
+          <t>0.3662</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr">
         <is>
-          <t>0.1101</t>
+          <t>0.116</t>
         </is>
       </c>
       <c r="AT174" t="inlineStr">
         <is>
-          <t>0.2855</t>
+          <t>0.3091</t>
         </is>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>68.96</t>
+          <t>70.66</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>13.72</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>41.74</t>
+          <t>42.81</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>21.31</t>
+          <t>27.13</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>0.1278</t>
+          <t>0.1444</t>
         </is>
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>38.63</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
         <is>
-          <t>88.42</t>
+          <t>89.46</t>
         </is>
       </c>
       <c r="BD174" t="inlineStr">
         <is>
-          <t>0.3966</t>
+          <t>0.3722</t>
         </is>
       </c>
       <c r="BE174" t="inlineStr">
         <is>
-          <t>0.1705</t>
+          <t>0.1568</t>
         </is>
       </c>
       <c r="BF174" t="inlineStr">
         <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="BG174" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH174" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
+          <t>33.3</t>
+        </is>
+      </c>
+      <c r="BG174" t="inlineStr"/>
+      <c r="BH174" t="inlineStr"/>
       <c r="BI174" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ174" t="inlineStr"/>
@@ -48983,47 +48979,47 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>669242</t>
+          <t>679845</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Nick Loftin</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-09-25T02:10:00Z</t>
+          <t>2026-09-24T18:10:00Z</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>David Sandlin</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>601713</t>
+          <t>689818</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -49032,7 +49028,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>35.5</v>
+        <v>35.4</v>
       </c>
       <c r="M175" t="inlineStr">
         <is>
@@ -49046,65 +49042,61 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P175" t="n">
-        <v>20.8</v>
+        <v>16.5</v>
       </c>
       <c r="Q175" t="n">
-        <v>42.7</v>
+        <v>31.5</v>
       </c>
       <c r="R175" t="n">
-        <v>27.6</v>
+        <v>30.2</v>
       </c>
       <c r="S175" t="n">
-        <v>40.2</v>
+        <v>76.2</v>
       </c>
       <c r="T175" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U175" t="n">
-        <v>37.4</v>
+        <v>54.9</v>
       </c>
       <c r="V175" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W175" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X175" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y175" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z175" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB175" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr"/>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD175" t="inlineStr"/>
@@ -49121,134 +49113,142 @@
       </c>
       <c r="AH175" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI175" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL175" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.6% barrel, 8.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN175" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>30.92</t>
         </is>
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>87.67</t>
+          <t>87.22</t>
         </is>
       </c>
       <c r="AQ175" t="inlineStr">
         <is>
-          <t>98.774</t>
+          <t>97.0725</t>
         </is>
       </c>
       <c r="AR175" t="inlineStr">
         <is>
-          <t>0.3662</t>
+          <t>0.3443</t>
         </is>
       </c>
       <c r="AS175" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>0.1144</t>
         </is>
       </c>
       <c r="AT175" t="inlineStr">
         <is>
-          <t>0.3091</t>
+          <t>0.294</t>
         </is>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>70.66</t>
+          <t>68.98</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>13.72</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>42.81</t>
+          <t>43.17</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>27.13</t>
+          <t>28.22</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>0.1444</t>
+          <t>0.1476</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>38.63</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>89.46</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="BD175" t="inlineStr">
         <is>
-          <t>0.3722</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BE175" t="inlineStr">
         <is>
-          <t>0.1568</t>
+          <t>0.153</t>
         </is>
       </c>
       <c r="BF175" t="inlineStr">
         <is>
-          <t>33.3</t>
-        </is>
-      </c>
-      <c r="BG175" t="inlineStr"/>
-      <c r="BH175" t="inlineStr"/>
+          <t>24.5</t>
+        </is>
+      </c>
+      <c r="BG175" t="inlineStr">
+        <is>
+          <t>In From RF</t>
+        </is>
+      </c>
+      <c r="BH175" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI175" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ175" t="inlineStr"/>
@@ -54052,7 +54052,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>31.1</v>
+        <v>31</v>
       </c>
       <c r="M193" t="inlineStr">
         <is>
@@ -54085,7 +54085,7 @@
         <v>80</v>
       </c>
       <c r="U193" t="n">
-        <v>12</v>
+        <v>10.1</v>
       </c>
       <c r="V193" t="inlineStr">
         <is>
@@ -54142,7 +54142,7 @@
       </c>
       <c r="AI193" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ193" t="inlineStr">
@@ -54152,7 +54152,7 @@
       </c>
       <c r="AK193" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/15, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL193" t="inlineStr">
